--- a/artfynd/A 51020-2025 artfynd.xlsx
+++ b/artfynd/A 51020-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105911417</v>
+        <v>97309092</v>
       </c>
       <c r="B2" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,50 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205995</v>
+        <v>3884</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541846.6672452593</v>
+        <v>541953</v>
       </c>
       <c r="R2" t="n">
-        <v>6507923.626285322</v>
+        <v>6507934</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105911348</v>
+        <v>105911387</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,25 +783,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>adult</t>
@@ -857,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541854.2162863025</v>
+        <v>541835</v>
       </c>
       <c r="R3" t="n">
-        <v>6507899.28911045</v>
+        <v>6507917</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -890,19 +861,9 @@
           <t>2021-08-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,42 +890,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105911424</v>
+        <v>105911348</v>
       </c>
       <c r="B4" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
@@ -982,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541901.4639377473</v>
+        <v>541854</v>
       </c>
       <c r="R4" t="n">
-        <v>6507861.871572202</v>
+        <v>6507899</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1015,19 +975,9 @@
           <t>2021-08-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,15 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105911387</v>
+        <v>105911417</v>
       </c>
       <c r="B5" t="n">
-        <v>57498</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,34 +1015,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
@@ -1115,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541834.7646038041</v>
+        <v>541847</v>
       </c>
       <c r="R5" t="n">
-        <v>6507917.263572175</v>
+        <v>6507924</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1148,19 +1085,9 @@
           <t>2021-08-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,6 +1111,116 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>105911424</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Finspång, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>541901</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6507862</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Amanda Sjölund</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Amanda Sjölund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51020-2025 artfynd.xlsx
+++ b/artfynd/A 51020-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97309092</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105911387</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105911348</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105911417</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,8 +1246,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105911424</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>